--- a/inmobiliarias-santiago/merge_ds49_categoria_primera.xlsx
+++ b/inmobiliarias-santiago/merge_ds49_categoria_primera.xlsx
@@ -551,7 +551,7 @@
     <row r="5" ht="70" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>73 destinatarios únicos: las entidades patrocinantes de categoría Primera habilitadas en la Región Metropolitana, según la nómina oficial MINVU de junio 2026. En la nómina son 75 filas, pero dos pares comparten casilla de correo, así que se deduplicó para no enviar dos veces al mismo buzón. Esas filas están marcadas en amarillo en la columna Nota.</t>
+          <t>73 destinatarios únicos: entidades patrocinantes de categoría Primera habilitadas en la Región Metropolitana, según la nómina oficial MINVU de junio 2026. En la nómina son 75 filas; la diferencia son casillas compartidas por dos entidades, deduplicadas para no enviar dos veces al mismo buzón (marcadas en amarillo en la columna Nota).</t>
         </is>
       </c>
     </row>
@@ -579,10 +579,10 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>{{comuna}}, {{telefono_1}}, {{rut}} — para tu registro y para el seguimiento telefónico.</t>
+          <t>{{comuna}}, {{telefono_1}}, {{rut}} — para tu registro y el seguimiento telefónico. La comuna es la de la oficina de la entidad, no la del terreno: no la uses en el cuerpo.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
     <row r="13" ht="70" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>En el PDF de MINVU el nombre de la persona y la dirección vienen en una sola celda, sin separador. La separación es una heurística y falla en algunos casos: hay nombres cortados y filas donde quedó texto de la dirección. NO la uses como campo de merge en el saludo — un nombre mal puesto arruina el correo. Sirve para saber por quién preguntar cuando llames por teléfono, y ahí conviene confirmarlo.</t>
+          <t>En el PDF de MINVU el nombre de la persona y la dirección vienen en una sola celda, sin separador. La separación es heurística y falla en algunos casos. NO la uses como campo de merge en el saludo. Sirve para saber por quién preguntar cuando llames, confirmándolo en la llamada.</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1. Reemplaza los datos del terreno y tu firma en la plantilla (plantilla_merge_ds49.md).</t>
+          <t>1. Reemplaza los datos del terreno y tu firma en plantilla_merge_ds49.md.</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>3. Tandas de 20 a 25 por día: son 73, o sea tres o cuatro días.</t>
+          <t>3. Tandas de 20 a 25 por día.</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>5. Muchos correos son de Gmail personal (gmail.com): son entidades chicas, y ahí el teléfono suele funcionar mejor que el correo.</t>
+          <t>5. 33 de los 73 correos son de casilla gratuita (Gmail y similares): entidades chicas, donde el teléfono suele rendir más que el correo.</t>
         </is>
       </c>
     </row>
